--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855661</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135888245</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855661</v>
       </c>
       <c r="B3" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135888245</v>
       </c>
       <c r="B4" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855661</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135888245</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855661</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135888245</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33817-2026 artfynd.xlsx
+++ b/artfynd/A 33817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135888244</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135855661</v>
       </c>
       <c r="B3" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135888245</v>
       </c>
       <c r="B4" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
